--- a/data/nzd0116/nzd0116.xlsx
+++ b/data/nzd0116/nzd0116.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E262"/>
+  <dimension ref="A1:E265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5932,6 +5932,69 @@
         <v>304.56</v>
       </c>
       <c r="E262" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>327.96</v>
+      </c>
+      <c r="C263" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="D263" t="n">
+        <v>305.65</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>321.03</v>
+      </c>
+      <c r="C264" t="n">
+        <v>297.07</v>
+      </c>
+      <c r="D264" t="n">
+        <v>298.63</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>321.03</v>
+      </c>
+      <c r="C265" t="n">
+        <v>298.46</v>
+      </c>
+      <c r="D265" t="n">
+        <v>299.47</v>
+      </c>
+      <c r="E265" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -5948,7 +6011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8881,6 +8944,36 @@
       </c>
       <c r="B293" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -9049,28 +9142,28 @@
         <v>0.0281</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01581337922758985</v>
+        <v>-0.06353092972533346</v>
       </c>
       <c r="J2" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K2" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001208914748676015</v>
+        <v>0.001770851617095448</v>
       </c>
       <c r="M2" t="n">
-        <v>8.599405595659716</v>
+        <v>8.866084391919646</v>
       </c>
       <c r="N2" t="n">
-        <v>115.415300039418</v>
+        <v>128.6229072647189</v>
       </c>
       <c r="O2" t="n">
-        <v>10.7431513085974</v>
+        <v>11.34120396010577</v>
       </c>
       <c r="P2" t="n">
-        <v>359.1563846353018</v>
+        <v>360.0047287391904</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9127,28 +9220,28 @@
         <v>0.0663</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2722379040518462</v>
+        <v>0.2181656100742168</v>
       </c>
       <c r="J3" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K3" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03207618376476473</v>
+        <v>0.02025330345454213</v>
       </c>
       <c r="M3" t="n">
-        <v>9.106557020471183</v>
+        <v>9.229424302533152</v>
       </c>
       <c r="N3" t="n">
-        <v>124.8009417466982</v>
+        <v>130.1638389376567</v>
       </c>
       <c r="O3" t="n">
-        <v>11.17143418486177</v>
+        <v>11.40893680137009</v>
       </c>
       <c r="P3" t="n">
-        <v>317.1659175329975</v>
+        <v>317.7440574426244</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9205,28 +9298,28 @@
         <v>0.0571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0411635649789177</v>
+        <v>-0.007813522833868346</v>
       </c>
       <c r="J4" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K4" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008135317572407486</v>
+        <v>2.866979087001731e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>8.339861575791993</v>
+        <v>8.441988029596891</v>
       </c>
       <c r="N4" t="n">
-        <v>114.9845498446317</v>
+        <v>119.1948852634481</v>
       </c>
       <c r="O4" t="n">
-        <v>10.72308490335834</v>
+        <v>10.91764101184171</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3234789223553</v>
+        <v>322.8510528301048</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -9264,7 +9357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E262"/>
+  <dimension ref="A1:E265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16337,6 +16430,87 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>-36.148214161273465,175.44027910120184</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>-36.148785980446824,175.44090106525292</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>-36.1491565150059,175.44167319463767</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>-36.148267584832226,175.4402392450348</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>-36.14883747685249,175.44086264688366</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>-36.149210632639,175.44163282102605</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>-36.148267584832226,175.4402392450348</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>-36.148826761283935,175.4408706411292</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>-36.1492041570254,175.44163765205934</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0116/nzd0116.xlsx
+++ b/data/nzd0116/nzd0116.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E265"/>
+  <dimension ref="A1:E266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5997,6 +5997,27 @@
       <c r="E265" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>331.16</v>
+      </c>
+      <c r="C266" t="n">
+        <v>301.94</v>
+      </c>
+      <c r="D266" t="n">
+        <v>303.23</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B296"/>
+  <dimension ref="A1:B297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8974,6 +8995,16 @@
       </c>
       <c r="B296" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -9142,28 +9173,28 @@
         <v>0.0281</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06353092972533346</v>
+        <v>-0.0832085937039885</v>
       </c>
       <c r="J2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001770851617095448</v>
+        <v>0.002994088479549073</v>
       </c>
       <c r="M2" t="n">
-        <v>8.866084391919646</v>
+        <v>8.92629698416517</v>
       </c>
       <c r="N2" t="n">
-        <v>128.6229072647189</v>
+        <v>130.8846400673144</v>
       </c>
       <c r="O2" t="n">
-        <v>11.34120396010577</v>
+        <v>11.44048251024905</v>
       </c>
       <c r="P2" t="n">
-        <v>360.0047287391904</v>
+        <v>360.2156484952196</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9220,28 +9251,28 @@
         <v>0.0663</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2181656100742168</v>
+        <v>0.2024602471704023</v>
       </c>
       <c r="J3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02025330345454213</v>
+        <v>0.0173982760977347</v>
       </c>
       <c r="M3" t="n">
-        <v>9.229424302533152</v>
+        <v>9.260754235086917</v>
       </c>
       <c r="N3" t="n">
-        <v>130.1638389376567</v>
+        <v>131.4225968170515</v>
       </c>
       <c r="O3" t="n">
-        <v>11.40893680137009</v>
+        <v>11.46396950523908</v>
       </c>
       <c r="P3" t="n">
-        <v>317.7440574426244</v>
+        <v>317.9123991378386</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9298,28 +9329,28 @@
         <v>0.0571</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.007813522833868346</v>
+        <v>-0.02201156453093651</v>
       </c>
       <c r="J4" t="n">
+        <v>265</v>
+      </c>
+      <c r="K4" t="n">
         <v>264</v>
       </c>
-      <c r="K4" t="n">
-        <v>263</v>
-      </c>
       <c r="L4" t="n">
-        <v>2.866979087001731e-05</v>
+        <v>0.0002266165769306827</v>
       </c>
       <c r="M4" t="n">
-        <v>8.441988029596891</v>
+        <v>8.470419520154044</v>
       </c>
       <c r="N4" t="n">
-        <v>119.1948852634481</v>
+        <v>120.1541442773118</v>
       </c>
       <c r="O4" t="n">
-        <v>10.91764101184171</v>
+        <v>10.96148458363701</v>
       </c>
       <c r="P4" t="n">
-        <v>322.8510528301048</v>
+        <v>323.0043674750553</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -9357,7 +9388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E265"/>
+  <dimension ref="A1:E266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16511,6 +16542,33 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>-36.148189492382365,175.44029750518615</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>-36.1487999338153,175.44089065549005</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>-36.14917517094343,175.44165927667513</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0116/nzd0116.xlsx
+++ b/data/nzd0116/nzd0116.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E266"/>
+  <dimension ref="A1:E267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6016,6 +6016,27 @@
         <v>303.23</v>
       </c>
       <c r="E266" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>331.16</v>
+      </c>
+      <c r="C267" t="n">
+        <v>303.99</v>
+      </c>
+      <c r="D267" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="E267" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -6032,7 +6053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B297"/>
+  <dimension ref="A1:B298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9005,6 +9026,16 @@
       </c>
       <c r="B297" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
@@ -9173,28 +9204,28 @@
         <v>0.0281</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0832085937039885</v>
+        <v>-0.1025051837719887</v>
       </c>
       <c r="J2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002994088479549073</v>
+        <v>0.004481211350167102</v>
       </c>
       <c r="M2" t="n">
-        <v>8.92629698416517</v>
+        <v>8.983881178244847</v>
       </c>
       <c r="N2" t="n">
-        <v>130.8846400673144</v>
+        <v>133.0652690964825</v>
       </c>
       <c r="O2" t="n">
-        <v>11.44048251024905</v>
+        <v>11.5353920217946</v>
       </c>
       <c r="P2" t="n">
-        <v>360.2156484952196</v>
+        <v>360.4228853504684</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9251,28 +9282,28 @@
         <v>0.0663</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2024602471704023</v>
+        <v>0.18852583209305</v>
       </c>
       <c r="J3" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K3" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0173982760977347</v>
+        <v>0.01508094533543924</v>
       </c>
       <c r="M3" t="n">
-        <v>9.260754235086917</v>
+        <v>9.284457039783447</v>
       </c>
       <c r="N3" t="n">
-        <v>131.4225968170515</v>
+        <v>132.3222058760109</v>
       </c>
       <c r="O3" t="n">
-        <v>11.46396950523908</v>
+        <v>11.50313895751985</v>
       </c>
       <c r="P3" t="n">
-        <v>317.9123991378386</v>
+        <v>318.0620486018209</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9329,28 +9360,28 @@
         <v>0.0571</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02201156453093651</v>
+        <v>-0.03415753341289039</v>
       </c>
       <c r="J4" t="n">
+        <v>266</v>
+      </c>
+      <c r="K4" t="n">
         <v>265</v>
       </c>
-      <c r="K4" t="n">
-        <v>264</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0002266165769306827</v>
+        <v>0.0005451293337869201</v>
       </c>
       <c r="M4" t="n">
-        <v>8.470419520154044</v>
+        <v>8.491858674250183</v>
       </c>
       <c r="N4" t="n">
-        <v>120.1541442773118</v>
+        <v>120.7452875287555</v>
       </c>
       <c r="O4" t="n">
-        <v>10.96148458363701</v>
+        <v>10.98841606095963</v>
       </c>
       <c r="P4" t="n">
-        <v>323.0043674750553</v>
+        <v>323.1357761029534</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -9388,7 +9419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E266"/>
+  <dimension ref="A1:E267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16569,6 +16600,33 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>-36.148189492382365,175.44029750518615</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>-36.14878413027636,175.4409024455527</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>-36.14915628373393,175.4416733671744</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
